--- a/SupplementalTables/DatCol_SupplementalTable_S2.xlsx
+++ b/SupplementalTables/DatCol_SupplementalTable_S2.xlsx
@@ -6,22 +6,22 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="S1A. Competition" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="S1B. Growth" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="S1C. Complementation" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="S1D. Cps" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="S1E. LDH" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="S2A. Competition" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="S2B. Growth" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="S2C. Complementation" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="S2D. Cps" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="S2E. LDH" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="199">
-  <si>
-    <t xml:space="preserve">Table S1A. HNO-ALI CFU Competition Analysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JE2 (Figure 1)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="211">
+  <si>
+    <t xml:space="preserve">Table S2A. HNO-ALI CFU Competition Analysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JE2 Strains (Figure 1)</t>
   </si>
   <si>
     <t xml:space="preserve">ANOVA Results</t>
@@ -156,7 +156,37 @@
     <t xml:space="preserve">alr1::Tn_vs_JE2-fmta::Tn_vs_JE2</t>
   </si>
   <si>
-    <t xml:space="preserve">Other (Figure 5)</t>
+    <t xml:space="preserve">t-Test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">statistic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parameter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">conf.low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">conf.high</t>
+  </si>
+  <si>
+    <t xml:space="preserve">method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">alternative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p.adj</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One Sample t-test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">two.sided</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other S. aureus Strains (Figure 5)</t>
   </si>
   <si>
     <t xml:space="preserve">p.value.adj</t>
@@ -171,7 +201,13 @@
     <t xml:space="preserve">alr1::Tn_vs_502a</t>
   </si>
   <si>
-    <t xml:space="preserve">Table S1B. Growth OD600</t>
+    <t xml:space="preserve">dat::Tn_vs_KPL4559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dat::Tn_vs_KPL2715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table S2B. Growth Curves OD600</t>
   </si>
   <si>
     <t xml:space="preserve">TSB (Figure S3A)</t>
@@ -336,10 +372,10 @@
     <t xml:space="preserve">CDM19 - ala (Figure S3C)</t>
   </si>
   <si>
-    <t xml:space="preserve">Table S1C. HNO-ALI CFU Complementation Analysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genetic (Figure 3B)</t>
+    <t xml:space="preserve">Table S2C. HNO-ALI CFU Complementation Analysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genetic Complementation (Figure 3B)</t>
   </si>
   <si>
     <t xml:space="preserve">JE2-dat</t>
@@ -453,7 +489,7 @@
     <t xml:space="preserve">dat-dat_37.5mM_Lglu</t>
   </si>
   <si>
-    <t xml:space="preserve">Chemical (Figure 4)</t>
+    <t xml:space="preserve">Chemical Complementation (Figure 4)</t>
   </si>
   <si>
     <t xml:space="preserve">vector</t>
@@ -522,7 +558,7 @@
     <t xml:space="preserve">pAB001</t>
   </si>
   <si>
-    <t xml:space="preserve">Table S1D. Coculture with Cps</t>
+    <t xml:space="preserve">Table S2D. S. aureus coculture with C. pseudodiphtheriticum</t>
   </si>
   <si>
     <t xml:space="preserve">(Figure 6)</t>
@@ -558,10 +594,10 @@
     <t xml:space="preserve">Coculture</t>
   </si>
   <si>
-    <t xml:space="preserve">Table S1C. Citotoxicity - LDH (Figure S1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hla (Figure S1A)</t>
+    <t xml:space="preserve">Table S2C. Citotoxicity - LDH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Damage is hla-dependent (Fig. S1A)</t>
   </si>
   <si>
     <t xml:space="preserve">nickname</t>
@@ -579,7 +615,7 @@
     <t xml:space="preserve">JE2hla::Tn</t>
   </si>
   <si>
-    <t xml:space="preserve">Tn (Figure S1B)</t>
+    <t xml:space="preserve">TnSeq Screen (Fig. S1B)</t>
   </si>
   <si>
     <t xml:space="preserve">Uncol-LAC</t>
@@ -594,7 +630,7 @@
     <t xml:space="preserve">LACTnLibrary</t>
   </si>
   <si>
-    <t xml:space="preserve">Other (Figure S1C)</t>
+    <t xml:space="preserve">Other S. aureus strains (Fig. S1C) </t>
   </si>
   <si>
     <t xml:space="preserve">Uncol-502a</t>
@@ -1080,7 +1116,7 @@
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="Q2" s="2" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="R2" s="2"/>
       <c r="S2" s="2"/>
@@ -1583,7 +1619,7 @@
         <v>38</v>
       </c>
       <c r="AF17" s="4" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18">
@@ -1639,7 +1675,7 @@
         <v>0.00355784522010743</v>
       </c>
       <c r="S18" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="T18" t="n">
         <v>-4.07791202682541</v>
@@ -1657,10 +1693,10 @@
         <v>0.00831103998520257</v>
       </c>
       <c r="Y18" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="Z18" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AA18" t="n">
         <v>0.0000713985558750553</v>
@@ -1772,6 +1808,361 @@
         <v>-2.18014205488699</v>
       </c>
       <c r="O20" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="Q21" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="R21" s="3"/>
+      <c r="S21" s="3"/>
+      <c r="T21" s="3"/>
+      <c r="U21" s="3"/>
+      <c r="V21" s="3"/>
+      <c r="W21" s="3"/>
+      <c r="X21" s="3"/>
+      <c r="Y21" s="3"/>
+      <c r="Z21" s="3"/>
+      <c r="AA21" s="3"/>
+      <c r="AB21" s="3"/>
+      <c r="AC21" s="3"/>
+      <c r="AD21" s="3"/>
+      <c r="AE21" s="3"/>
+      <c r="AF21" s="3"/>
+    </row>
+    <row r="22">
+      <c r="Q22" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="R22" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="S22" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="T22" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="U22" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="V22" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="W22" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="X22" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y22" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z22" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="AA22" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB22" s="4"/>
+      <c r="AC22" s="4"/>
+      <c r="AD22" s="4"/>
+      <c r="AE22" s="4"/>
+      <c r="AF22" s="4"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="3"/>
+      <c r="N23" s="3"/>
+      <c r="O23" s="3"/>
+      <c r="Q23" t="s">
+        <v>59</v>
+      </c>
+      <c r="R23" t="n">
+        <v>-9.54723291466284</v>
+      </c>
+      <c r="S23" t="n">
+        <v>-31.3245258588893</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.00101757798217919</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
+      </c>
+      <c r="V23" t="n">
+        <v>-10.9959724964209</v>
+      </c>
+      <c r="W23" t="n">
+        <v>-8.09849333290476</v>
+      </c>
+      <c r="X23" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0.00407031192871678</v>
+      </c>
+      <c r="AA23" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="L24" s="4"/>
+      <c r="M24" s="4"/>
+      <c r="N24" s="4"/>
+      <c r="O24" s="4"/>
+      <c r="Q24" t="s">
+        <v>60</v>
+      </c>
+      <c r="R24" t="n">
+        <v>-5.46932088783743</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-21.6846559599771</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.00211988467834468</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-6.7529585544462</v>
+      </c>
+      <c r="W24" t="n">
+        <v>-4.18568322122866</v>
+      </c>
+      <c r="X24" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0.00635965403503405</v>
+      </c>
+      <c r="AA24" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" t="n">
+        <v>-7.1655702644133</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-15.0238142425596</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.000023659500391069</v>
+      </c>
+      <c r="E25" t="n">
+        <v>5</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-8.56270326009768</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-5.76843726872893</v>
+      </c>
+      <c r="H25" t="s">
+        <v>54</v>
+      </c>
+      <c r="I25" t="s">
+        <v>55</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.000070978501173207</v>
+      </c>
+      <c r="K25" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>61</v>
+      </c>
+      <c r="R25" t="n">
+        <v>-6.75051619840668</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-17.8116463161247</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.00313721593695603</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-8.62276197996886</v>
+      </c>
+      <c r="W25" t="n">
+        <v>-4.87827041684451</v>
+      </c>
+      <c r="X25" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0.00635965403503405</v>
+      </c>
+      <c r="AA25" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" t="n">
+        <v>-3.6307108997675</v>
+      </c>
+      <c r="C26" t="n">
+        <v>-13.9837042538213</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.0000336268715984752</v>
+      </c>
+      <c r="E26" t="n">
+        <v>5</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-4.48196040483141</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-2.77946139470359</v>
+      </c>
+      <c r="H26" t="s">
+        <v>54</v>
+      </c>
+      <c r="I26" t="s">
+        <v>55</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.000070978501173207</v>
+      </c>
+      <c r="K26" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>62</v>
+      </c>
+      <c r="R26" t="n">
+        <v>-8.07122275110851</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-10.4559696270156</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.00902323199553175</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
+      </c>
+      <c r="V26" t="n">
+        <v>-11.8040493300398</v>
+      </c>
+      <c r="W26" t="n">
+        <v>-4.3383961721772</v>
+      </c>
+      <c r="X26" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0.00902323199553175</v>
+      </c>
+      <c r="AA26" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>44</v>
+      </c>
+      <c r="B27" t="n">
+        <v>-2.11955158120242</v>
+      </c>
+      <c r="C27" t="n">
+        <v>-7.83583797711333</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.00432832267707844</v>
+      </c>
+      <c r="E27" t="n">
+        <v>3</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-3.38652588985152</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-0.852577272553309</v>
+      </c>
+      <c r="H27" t="s">
+        <v>54</v>
+      </c>
+      <c r="I27" t="s">
+        <v>55</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.00432832267707844</v>
+      </c>
+      <c r="K27" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1825,7 +2216,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1844,7 +2235,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1862,7 +2253,7 @@
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
       <c r="R2" s="2" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="S2" s="2"/>
       <c r="T2" s="2"/>
@@ -1880,7 +2271,7 @@
       <c r="AF2" s="2"/>
       <c r="AG2" s="2"/>
       <c r="AI2" s="2" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="AJ2" s="2"/>
       <c r="AK2" s="2"/>
@@ -2048,7 +2439,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B6" t="n">
         <v>50.1446900769212</v>
@@ -2069,7 +2460,7 @@
         <v>0.000262304679650516</v>
       </c>
       <c r="R6" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="S6" t="n">
         <v>4.22068393589757</v>
@@ -2090,7 +2481,7 @@
         <v>0.103848010309764</v>
       </c>
       <c r="AI6" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="AJ6" t="n">
         <v>1297.17597491025</v>
@@ -2261,7 +2652,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="B11" t="s">
         <v>20</v>
@@ -2280,7 +2671,7 @@
         <v>0</v>
       </c>
       <c r="R11" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="S11" t="s">
         <v>20</v>
@@ -2299,7 +2690,7 @@
         <v>0</v>
       </c>
       <c r="AI11" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="AJ11" t="s">
         <v>20</v>
@@ -2474,7 +2865,7 @@
         <v>38</v>
       </c>
       <c r="P16" s="4" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="R16" s="4" t="s">
         <v>24</v>
@@ -2522,7 +2913,7 @@
         <v>38</v>
       </c>
       <c r="AG16" s="4" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="AI16" s="4" t="s">
         <v>24</v>
@@ -2570,18 +2961,18 @@
         <v>38</v>
       </c>
       <c r="AX16" s="4" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B17" t="n">
         <v>0.000262304679650516</v>
       </c>
       <c r="C17" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D17" t="n">
         <v>0.663999999999938</v>
@@ -2599,10 +2990,10 @@
         <v>0.369197221897624</v>
       </c>
       <c r="I17" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="J17" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="K17" t="n">
         <v>23.5504999999997</v>
@@ -2623,13 +3014,13 @@
         <v>1</v>
       </c>
       <c r="R17" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="S17" t="n">
         <v>0.103848010309764</v>
       </c>
       <c r="T17" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="U17" t="n">
         <v>-0.277999999999932</v>
@@ -2647,10 +3038,10 @@
         <v>0.447078888120274</v>
       </c>
       <c r="Z17" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="AA17" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="AB17" t="n">
         <v>17.9626666666668</v>
@@ -2671,13 +3062,13 @@
         <v>1</v>
       </c>
       <c r="AI17" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="AJ17" t="n">
         <v>0.00000000000000000000219073928843663</v>
       </c>
       <c r="AK17" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="AL17" t="n">
         <v>0.162500000000055</v>
@@ -2695,10 +3086,10 @@
         <v>0.781212307703184</v>
       </c>
       <c r="AQ17" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="AR17" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="AS17" t="n">
         <v>2.72950000000005</v>
@@ -2721,13 +3112,13 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B18" t="n">
         <v>0.000262304679650516</v>
       </c>
       <c r="C18" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="D18" t="n">
         <v>0.117999999999984</v>
@@ -2745,10 +3136,10 @@
         <v>0.872164469530275</v>
       </c>
       <c r="I18" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="J18" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="K18" t="n">
         <v>23.5504999999997</v>
@@ -2769,13 +3160,13 @@
         <v>1</v>
       </c>
       <c r="R18" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="S18" t="n">
         <v>0.103848010309764</v>
       </c>
       <c r="T18" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="U18" t="n">
         <v>-0.018833333333302</v>
@@ -2793,10 +3184,10 @@
         <v>0.958670205282023</v>
       </c>
       <c r="Z18" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="AA18" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="AB18" t="n">
         <v>17.9626666666668</v>
@@ -2817,13 +3208,13 @@
         <v>1</v>
       </c>
       <c r="AI18" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="AJ18" t="n">
         <v>0.00000000000000000000219073928843663</v>
       </c>
       <c r="AK18" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="AL18" t="n">
         <v>0.117166666666724</v>
@@ -2841,10 +3232,10 @@
         <v>0.84121787704993</v>
       </c>
       <c r="AQ18" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="AR18" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="AS18" t="n">
         <v>2.72950000000005</v>
@@ -2867,13 +3258,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B19" t="n">
         <v>0.000262304679650516</v>
       </c>
       <c r="C19" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="D19" t="n">
         <v>0.244166666666613</v>
@@ -2891,10 +3282,10 @@
         <v>0.739393354610986</v>
       </c>
       <c r="I19" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="J19" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="K19" t="n">
         <v>23.5504999999997</v>
@@ -2915,13 +3306,13 @@
         <v>1</v>
       </c>
       <c r="R19" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="S19" t="n">
         <v>0.103848010309764</v>
       </c>
       <c r="T19" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="U19" t="n">
         <v>-0.212499999999936</v>
@@ -2939,10 +3330,10 @@
         <v>0.56013835731113</v>
       </c>
       <c r="Z19" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="AA19" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="AB19" t="n">
         <v>17.9626666666668</v>
@@ -2963,13 +3354,13 @@
         <v>1</v>
       </c>
       <c r="AI19" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="AJ19" t="n">
         <v>0.00000000000000000000219073928843663</v>
       </c>
       <c r="AK19" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="AL19" t="n">
         <v>0.307666666666721</v>
@@ -2987,10 +3378,10 @@
         <v>0.599757954618625</v>
       </c>
       <c r="AQ19" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="AR19" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="AS19" t="n">
         <v>2.72950000000005</v>
@@ -3013,13 +3404,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B20" t="n">
         <v>0.000262304679650516</v>
       </c>
       <c r="C20" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="D20" t="n">
         <v>1.26816666666659</v>
@@ -3037,10 +3428,10 @@
         <v>0.0932638998184275</v>
       </c>
       <c r="I20" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="J20" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="K20" t="n">
         <v>23.5504999999997</v>
@@ -3061,13 +3452,13 @@
         <v>1</v>
       </c>
       <c r="R20" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="S20" t="n">
         <v>0.103848010309764</v>
       </c>
       <c r="T20" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="U20" t="n">
         <v>0.199500000000079</v>
@@ -3085,10 +3476,10 @@
         <v>0.584224228566868</v>
       </c>
       <c r="Z20" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="AA20" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="AB20" t="n">
         <v>17.9626666666668</v>
@@ -3109,13 +3500,13 @@
         <v>1</v>
       </c>
       <c r="AI20" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="AJ20" t="n">
         <v>0.00000000000000000000219073928843663</v>
       </c>
       <c r="AK20" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="AL20" t="n">
         <v>-13.9316666666666</v>
@@ -3133,10 +3524,10 @@
         <v>0.00000000000000000255062472958946</v>
       </c>
       <c r="AQ20" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="AR20" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="AS20" t="n">
         <v>2.72950000000005</v>
@@ -3159,13 +3550,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B21" t="n">
         <v>0.000262304679650516</v>
       </c>
       <c r="C21" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="D21" t="n">
         <v>1.21116666666663</v>
@@ -3183,10 +3574,10 @@
         <v>0.108043303751894</v>
       </c>
       <c r="I21" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="J21" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="K21" t="n">
         <v>23.5504999999997</v>
@@ -3207,13 +3598,13 @@
         <v>1</v>
       </c>
       <c r="R21" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="S21" t="n">
         <v>0.103848010309764</v>
       </c>
       <c r="T21" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="U21" t="n">
         <v>-0.135166666666622</v>
@@ -3231,10 +3622,10 @@
         <v>0.71034266516898</v>
       </c>
       <c r="Z21" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="AA21" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="AB21" t="n">
         <v>17.9626666666668</v>
@@ -3255,13 +3646,13 @@
         <v>1</v>
       </c>
       <c r="AI21" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="AJ21" t="n">
         <v>0.00000000000000000000219073928843663</v>
       </c>
       <c r="AK21" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="AL21" t="n">
         <v>-10.0169999999999</v>
@@ -3279,10 +3670,10 @@
         <v>0.00000000000000459491196761647</v>
       </c>
       <c r="AQ21" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="AR21" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="AS21" t="n">
         <v>2.72950000000005</v>
@@ -3305,13 +3696,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B22" t="n">
         <v>0.000262304679650516</v>
       </c>
       <c r="C22" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="D22" t="n">
         <v>0.801166666666573</v>
@@ -3329,10 +3720,10 @@
         <v>0.280435813848229</v>
       </c>
       <c r="I22" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="J22" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="K22" t="n">
         <v>23.5504999999997</v>
@@ -3353,13 +3744,13 @@
         <v>1</v>
       </c>
       <c r="R22" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="S22" t="n">
         <v>0.103848010309764</v>
       </c>
       <c r="T22" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="U22" t="n">
         <v>-0.248500000000004</v>
@@ -3377,10 +3768,10 @@
         <v>0.49622122322045</v>
       </c>
       <c r="Z22" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="AA22" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="AB22" t="n">
         <v>17.9626666666668</v>
@@ -3401,13 +3792,13 @@
         <v>1</v>
       </c>
       <c r="AI22" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="AJ22" t="n">
         <v>0.00000000000000000000219073928843663</v>
       </c>
       <c r="AK22" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="AL22" t="n">
         <v>-9.87166666666656</v>
@@ -3425,10 +3816,10 @@
         <v>0.00000000000000636212033426231</v>
       </c>
       <c r="AQ22" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="AR22" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="AS22" t="n">
         <v>2.72950000000005</v>
@@ -3451,13 +3842,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B23" t="n">
         <v>0.000262304679650516</v>
       </c>
       <c r="C23" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="D23" t="n">
         <v>-0.545999999999954</v>
@@ -3475,10 +3866,10 @@
         <v>0.459039113305618</v>
       </c>
       <c r="I23" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="J23" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="K23" t="n">
         <v>22.8864999999997</v>
@@ -3499,13 +3890,13 @@
         <v>1</v>
       </c>
       <c r="R23" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="S23" t="n">
         <v>0.103848010309764</v>
       </c>
       <c r="T23" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="U23" t="n">
         <v>0.25916666666663</v>
@@ -3523,10 +3914,10 @@
         <v>0.478106083967312</v>
       </c>
       <c r="Z23" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="AA23" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="AB23" t="n">
         <v>18.2406666666667</v>
@@ -3547,13 +3938,13 @@
         <v>1</v>
       </c>
       <c r="AI23" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="AJ23" t="n">
         <v>0.00000000000000000000219073928843663</v>
       </c>
       <c r="AK23" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="AL23" t="n">
         <v>-0.045333333333331</v>
@@ -3571,10 +3962,10 @@
         <v>0.938193450048168</v>
       </c>
       <c r="AQ23" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="AR23" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="AS23" t="n">
         <v>2.567</v>
@@ -3597,13 +3988,13 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B24" t="n">
         <v>0.000262304679650516</v>
       </c>
       <c r="C24" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="D24" t="n">
         <v>-0.419833333333325</v>
@@ -3621,10 +4012,10 @@
         <v>0.568213795367487</v>
       </c>
       <c r="I24" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="J24" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="K24" t="n">
         <v>22.8864999999997</v>
@@ -3645,13 +4036,13 @@
         <v>1</v>
       </c>
       <c r="R24" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="S24" t="n">
         <v>0.103848010309764</v>
       </c>
       <c r="T24" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="U24" t="n">
         <v>0.0654999999999954</v>
@@ -3669,10 +4060,10 @@
         <v>0.8570151711463</v>
       </c>
       <c r="Z24" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="AA24" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="AB24" t="n">
         <v>18.2406666666667</v>
@@ -3693,13 +4084,13 @@
         <v>1</v>
       </c>
       <c r="AI24" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="AJ24" t="n">
         <v>0.00000000000000000000219073928843663</v>
       </c>
       <c r="AK24" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="AL24" t="n">
         <v>0.145166666666666</v>
@@ -3717,10 +4108,10 @@
         <v>0.804014542871909</v>
       </c>
       <c r="AQ24" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="AR24" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="AS24" t="n">
         <v>2.567</v>
@@ -3743,13 +4134,13 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B25" t="n">
         <v>0.000262304679650516</v>
       </c>
       <c r="C25" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="D25" t="n">
         <v>0.604166666666648</v>
@@ -3767,10 +4158,10 @@
         <v>0.413212908622888</v>
       </c>
       <c r="I25" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="J25" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="K25" t="n">
         <v>22.8864999999997</v>
@@ -3791,13 +4182,13 @@
         <v>1</v>
       </c>
       <c r="R25" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="S25" t="n">
         <v>0.103848010309764</v>
       </c>
       <c r="T25" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="U25" t="n">
         <v>0.477500000000011</v>
@@ -3815,10 +4206,10 @@
         <v>0.196769355644683</v>
       </c>
       <c r="Z25" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="AA25" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="AB25" t="n">
         <v>18.2406666666667</v>
@@ -3839,13 +4230,13 @@
         <v>1</v>
       </c>
       <c r="AI25" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="AJ25" t="n">
         <v>0.00000000000000000000219073928843663</v>
       </c>
       <c r="AK25" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="AL25" t="n">
         <v>-14.0941666666667</v>
@@ -3863,10 +4254,10 @@
         <v>0.00000000000000000195138633757401</v>
       </c>
       <c r="AQ25" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="AR25" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="AS25" t="n">
         <v>2.567</v>
@@ -3889,13 +4280,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B26" t="n">
         <v>0.000262304679650516</v>
       </c>
       <c r="C26" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="D26" t="n">
         <v>0.547166666666688</v>
@@ -3913,10 +4304,10 @@
         <v>0.458091075071469</v>
       </c>
       <c r="I26" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="J26" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="K26" t="n">
         <v>22.8864999999997</v>
@@ -3937,13 +4328,13 @@
         <v>1</v>
       </c>
       <c r="R26" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="S26" t="n">
         <v>0.103848010309764</v>
       </c>
       <c r="T26" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="U26" t="n">
         <v>0.14283333333331</v>
@@ -3961,10 +4352,10 @@
         <v>0.694766558569571</v>
       </c>
       <c r="Z26" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="AA26" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="AB26" t="n">
         <v>18.2406666666667</v>
@@ -3985,13 +4376,13 @@
         <v>1</v>
       </c>
       <c r="AI26" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="AJ26" t="n">
         <v>0.00000000000000000000219073928843663</v>
       </c>
       <c r="AK26" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="AL26" t="n">
         <v>-10.1795</v>
@@ -4009,10 +4400,10 @@
         <v>0.00000000000000320868791957431</v>
       </c>
       <c r="AQ26" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="AR26" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="AS26" t="n">
         <v>2.567</v>
@@ -4035,13 +4426,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B27" t="n">
         <v>0.000262304679650516</v>
       </c>
       <c r="C27" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="D27" t="n">
         <v>0.137166666666635</v>
@@ -4059,10 +4450,10 @@
         <v>0.851638504822646</v>
       </c>
       <c r="I27" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="J27" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="K27" t="n">
         <v>22.8864999999997</v>
@@ -4083,13 +4474,13 @@
         <v>1</v>
       </c>
       <c r="R27" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="S27" t="n">
         <v>0.103848010309764</v>
       </c>
       <c r="T27" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="U27" t="n">
         <v>0.0294999999999277</v>
@@ -4107,10 +4498,10 @@
         <v>0.935306928046384</v>
       </c>
       <c r="Z27" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="AA27" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="AB27" t="n">
         <v>18.2406666666667</v>
@@ -4131,13 +4522,13 @@
         <v>1</v>
       </c>
       <c r="AI27" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="AJ27" t="n">
         <v>0.00000000000000000000219073928843663</v>
       </c>
       <c r="AK27" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="AL27" t="n">
         <v>-10.0341666666666</v>
@@ -4155,10 +4546,10 @@
         <v>0.00000000000000442282976888534</v>
       </c>
       <c r="AQ27" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="AR27" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="AS27" t="n">
         <v>2.567</v>
@@ -4181,13 +4572,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B28" t="n">
         <v>0.000262304679650516</v>
       </c>
       <c r="C28" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="D28" t="n">
         <v>0.12616666666663</v>
@@ -4205,10 +4596,10 @@
         <v>0.863406538628347</v>
       </c>
       <c r="I28" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="J28" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="K28" t="n">
         <v>23.4324999999997</v>
@@ -4229,13 +4620,13 @@
         <v>1</v>
       </c>
       <c r="R28" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="S28" t="n">
         <v>0.103848010309764</v>
       </c>
       <c r="T28" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="U28" t="n">
         <v>-0.193666666666635</v>
@@ -4253,10 +4644,10 @@
         <v>0.595196387947071</v>
       </c>
       <c r="Z28" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="AA28" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="AB28" t="n">
         <v>17.9815000000001</v>
@@ -4277,13 +4668,13 @@
         <v>1</v>
       </c>
       <c r="AI28" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="AJ28" t="n">
         <v>0.00000000000000000000219073928843663</v>
       </c>
       <c r="AK28" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="AL28" t="n">
         <v>0.190499999999997</v>
@@ -4301,10 +4692,10 @@
         <v>0.74480515249479</v>
       </c>
       <c r="AQ28" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="AR28" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="AS28" t="n">
         <v>2.61233333333333</v>
@@ -4327,13 +4718,13 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B29" t="n">
         <v>0.000262304679650516</v>
       </c>
       <c r="C29" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="D29" t="n">
         <v>1.1501666666666</v>
@@ -4351,10 +4742,10 @@
         <v>0.125994693072378</v>
       </c>
       <c r="I29" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="J29" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="K29" t="n">
         <v>23.4324999999997</v>
@@ -4375,13 +4766,13 @@
         <v>1</v>
       </c>
       <c r="R29" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="S29" t="n">
         <v>0.103848010309764</v>
       </c>
       <c r="T29" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="U29" t="n">
         <v>0.218333333333381</v>
@@ -4399,10 +4790,10 @@
         <v>0.549499218388062</v>
       </c>
       <c r="Z29" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="AA29" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="AB29" t="n">
         <v>17.9815000000001</v>
@@ -4423,13 +4814,13 @@
         <v>1</v>
       </c>
       <c r="AI29" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="AJ29" t="n">
         <v>0.00000000000000000000219073928843663</v>
       </c>
       <c r="AK29" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="AL29" t="n">
         <v>-14.0488333333334</v>
@@ -4447,10 +4838,10 @@
         <v>0.00000000000000000210214990740466</v>
       </c>
       <c r="AQ29" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="AR29" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="AS29" t="n">
         <v>2.61233333333333</v>
@@ -4473,13 +4864,13 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B30" t="n">
         <v>0.000262304679650516</v>
       </c>
       <c r="C30" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="D30" t="n">
         <v>1.09316666666664</v>
@@ -4497,10 +4888,10 @@
         <v>0.144936419117237</v>
       </c>
       <c r="I30" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="J30" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="K30" t="n">
         <v>23.4324999999997</v>
@@ -4521,13 +4912,13 @@
         <v>1</v>
       </c>
       <c r="R30" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="S30" t="n">
         <v>0.103848010309764</v>
       </c>
       <c r="T30" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="U30" t="n">
         <v>-0.11633333333332</v>
@@ -4545,10 +4936,10 @@
         <v>0.749143609475093</v>
       </c>
       <c r="Z30" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="AA30" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="AB30" t="n">
         <v>17.9815000000001</v>
@@ -4569,13 +4960,13 @@
         <v>1</v>
       </c>
       <c r="AI30" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="AJ30" t="n">
         <v>0.00000000000000000000219073928843663</v>
       </c>
       <c r="AK30" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="AL30" t="n">
         <v>-10.1341666666666</v>
@@ -4593,10 +4984,10 @@
         <v>0.00000000000000354500466522421</v>
       </c>
       <c r="AQ30" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="AR30" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="AS30" t="n">
         <v>2.61233333333333</v>
@@ -4619,13 +5010,13 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B31" t="n">
         <v>0.000262304679650516</v>
       </c>
       <c r="C31" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="D31" t="n">
         <v>0.683166666666589</v>
@@ -4643,10 +5034,10 @@
         <v>0.355776910031264</v>
       </c>
       <c r="I31" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="J31" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="K31" t="n">
         <v>23.4324999999997</v>
@@ -4667,13 +5058,13 @@
         <v>1</v>
       </c>
       <c r="R31" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="S31" t="n">
         <v>0.103848010309764</v>
       </c>
       <c r="T31" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="U31" t="n">
         <v>-0.229666666666702</v>
@@ -4691,10 +5082,10 @@
         <v>0.529136064995058</v>
       </c>
       <c r="Z31" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="AA31" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="AB31" t="n">
         <v>17.9815000000001</v>
@@ -4715,13 +5106,13 @@
         <v>1</v>
       </c>
       <c r="AI31" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="AJ31" t="n">
         <v>0.00000000000000000000219073928843663</v>
       </c>
       <c r="AK31" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="AL31" t="n">
         <v>-9.98883333333328</v>
@@ -4739,10 +5130,10 @@
         <v>0.00000000000000489248123439398</v>
       </c>
       <c r="AQ31" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="AR31" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="AS31" t="n">
         <v>2.61233333333333</v>
@@ -4765,13 +5156,13 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B32" t="n">
         <v>0.000262304679650516</v>
       </c>
       <c r="C32" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="D32" t="n">
         <v>1.02399999999997</v>
@@ -4789,10 +5180,10 @@
         <v>0.170967533666344</v>
       </c>
       <c r="I32" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="J32" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="K32" t="n">
         <v>23.3063333333331</v>
@@ -4813,13 +5204,13 @@
         <v>1</v>
       </c>
       <c r="R32" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="S32" t="n">
         <v>0.103848010309764</v>
       </c>
       <c r="T32" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="U32" t="n">
         <v>0.412000000000016</v>
@@ -4837,10 +5228,10 @@
         <v>0.263267191047187</v>
       </c>
       <c r="Z32" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="AA32" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="AB32" t="n">
         <v>18.1751666666667</v>
@@ -4861,13 +5252,13 @@
         <v>1</v>
       </c>
       <c r="AI32" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="AJ32" t="n">
         <v>0.00000000000000000000219073928843663</v>
       </c>
       <c r="AK32" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="AL32" t="n">
         <v>-14.2393333333334</v>
@@ -4885,10 +5276,10 @@
         <v>0.00000000000000000153989176707534</v>
       </c>
       <c r="AQ32" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="AR32" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="AS32" t="n">
         <v>2.42183333333333</v>
@@ -4911,13 +5302,13 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B33" t="n">
         <v>0.000262304679650516</v>
       </c>
       <c r="C33" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="D33" t="n">
         <v>0.967000000000013</v>
@@ -4935,10 +5326,10 @@
         <v>0.195109473685213</v>
       </c>
       <c r="I33" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="J33" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="K33" t="n">
         <v>23.3063333333331</v>
@@ -4959,13 +5350,13 @@
         <v>1</v>
       </c>
       <c r="R33" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="S33" t="n">
         <v>0.103848010309764</v>
       </c>
       <c r="T33" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="U33" t="n">
         <v>0.0773333333333142</v>
@@ -4983,10 +5374,10 @@
         <v>0.831563378662024</v>
       </c>
       <c r="Z33" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="AA33" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="AB33" t="n">
         <v>18.1751666666667</v>
@@ -5007,13 +5398,13 @@
         <v>1</v>
       </c>
       <c r="AI33" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="AJ33" t="n">
         <v>0.00000000000000000000219073928843663</v>
       </c>
       <c r="AK33" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="AL33" t="n">
         <v>-10.3246666666666</v>
@@ -5031,10 +5422,10 @@
         <v>0.0000000000000023378486457162</v>
       </c>
       <c r="AQ33" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="AR33" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="AS33" t="n">
         <v>2.42183333333333</v>
@@ -5057,13 +5448,13 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B34" t="n">
         <v>0.000262304679650516</v>
       </c>
       <c r="C34" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="D34" t="n">
         <v>0.55699999999996</v>
@@ -5081,10 +5472,10 @@
         <v>0.450147012773712</v>
       </c>
       <c r="I34" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="J34" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="K34" t="n">
         <v>23.3063333333331</v>
@@ -5105,13 +5496,13 @@
         <v>1</v>
       </c>
       <c r="R34" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="S34" t="n">
         <v>0.103848010309764</v>
       </c>
       <c r="T34" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="U34" t="n">
         <v>-0.0360000000000677</v>
@@ -5129,10 +5520,10 @@
         <v>0.92109756264894</v>
       </c>
       <c r="Z34" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="AA34" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="AB34" t="n">
         <v>18.1751666666667</v>
@@ -5153,13 +5544,13 @@
         <v>1</v>
       </c>
       <c r="AI34" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="AJ34" t="n">
         <v>0.00000000000000000000219073928843663</v>
       </c>
       <c r="AK34" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AL34" t="n">
         <v>-10.1793333333333</v>
@@ -5177,10 +5568,10 @@
         <v>0.00000000000000320986174338893</v>
       </c>
       <c r="AQ34" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="AR34" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="AS34" t="n">
         <v>2.42183333333333</v>
@@ -5203,13 +5594,13 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B35" t="n">
         <v>0.000262304679650516</v>
       </c>
       <c r="C35" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="D35" t="n">
         <v>-0.0569999999999595</v>
@@ -5227,10 +5618,10 @@
         <v>0.938031730436134</v>
       </c>
       <c r="I35" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="J35" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="K35" t="n">
         <v>22.2823333333331</v>
@@ -5251,13 +5642,13 @@
         <v>1</v>
       </c>
       <c r="R35" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="S35" t="n">
         <v>0.103848010309764</v>
       </c>
       <c r="T35" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="U35" t="n">
         <v>-0.334666666666701</v>
@@ -5275,10 +5666,10 @@
         <v>0.361354930039485</v>
       </c>
       <c r="Z35" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="AA35" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="AB35" t="n">
         <v>17.7631666666667</v>
@@ -5299,13 +5690,13 @@
         <v>1</v>
       </c>
       <c r="AI35" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="AJ35" t="n">
         <v>0.00000000000000000000219073928843663</v>
       </c>
       <c r="AK35" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="AL35" t="n">
         <v>3.91466666666672</v>
@@ -5323,10 +5714,10 @@
         <v>0.000000534458631654227</v>
       </c>
       <c r="AQ35" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="AR35" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="AS35" t="n">
         <v>16.6611666666667</v>
@@ -5349,13 +5740,13 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B36" t="n">
         <v>0.000262304679650516</v>
       </c>
       <c r="C36" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="D36" t="n">
         <v>-0.467000000000013</v>
@@ -5373,10 +5764,10 @@
         <v>0.525897051820289</v>
       </c>
       <c r="I36" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="J36" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="K36" t="n">
         <v>22.2823333333331</v>
@@ -5397,13 +5788,13 @@
         <v>1</v>
       </c>
       <c r="R36" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="S36" t="n">
         <v>0.103848010309764</v>
       </c>
       <c r="T36" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="U36" t="n">
         <v>-0.448000000000083</v>
@@ -5421,10 +5812,10 @@
         <v>0.224909464031128</v>
       </c>
       <c r="Z36" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="AA36" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="AB36" t="n">
         <v>17.7631666666667</v>
@@ -5445,13 +5836,13 @@
         <v>1</v>
       </c>
       <c r="AI36" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="AJ36" t="n">
         <v>0.00000000000000000000219073928843663</v>
       </c>
       <c r="AK36" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AL36" t="n">
         <v>4.06000000000008</v>
@@ -5469,10 +5860,10 @@
         <v>0.000000295655735356949</v>
       </c>
       <c r="AQ36" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="AR36" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="AS36" t="n">
         <v>16.6611666666667</v>
@@ -5495,13 +5886,13 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B37" t="n">
         <v>0.000262304679650516</v>
       </c>
       <c r="C37" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="D37" t="n">
         <v>-0.915333333333327</v>
@@ -5519,10 +5910,10 @@
         <v>0.219217518788734</v>
       </c>
       <c r="I37" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="J37" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K37" t="n">
         <v>22.339333333333</v>
@@ -5543,13 +5934,13 @@
         <v>1</v>
       </c>
       <c r="R37" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="S37" t="n">
         <v>0.103848010309764</v>
       </c>
       <c r="T37" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="U37" t="n">
         <v>0.121166666666634</v>
@@ -5567,10 +5958,10 @@
         <v>0.739116357285975</v>
       </c>
       <c r="Z37" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="AA37" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AB37" t="n">
         <v>18.0978333333334</v>
@@ -5591,13 +5982,13 @@
         <v>1</v>
       </c>
       <c r="AI37" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="AJ37" t="n">
         <v>0.00000000000000000000219073928843663</v>
       </c>
       <c r="AK37" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AL37" t="n">
         <v>-0.508000000000008</v>
@@ -5615,10 +6006,10 @@
         <v>0.38861543123728</v>
       </c>
       <c r="AQ37" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="AR37" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AS37" t="n">
         <v>12.7465</v>
@@ -5641,13 +6032,13 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B38" t="n">
         <v>0.000262304679650516</v>
       </c>
       <c r="C38" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="D38" t="n">
         <v>-0.410000000000053</v>
@@ -5665,10 +6056,10 @@
         <v>0.577249915693489</v>
       </c>
       <c r="I38" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="J38" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="K38" t="n">
         <v>22.339333333333</v>
@@ -5689,13 +6080,13 @@
         <v>1</v>
       </c>
       <c r="R38" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="S38" t="n">
         <v>0.103848010309764</v>
       </c>
       <c r="T38" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="U38" t="n">
         <v>-0.113333333333382</v>
@@ -5713,10 +6104,10 @@
         <v>0.755390316814935</v>
       </c>
       <c r="Z38" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="AA38" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="AB38" t="n">
         <v>18.0978333333334</v>
@@ -5737,13 +6128,13 @@
         <v>1</v>
       </c>
       <c r="AI38" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="AJ38" t="n">
         <v>0.00000000000000000000219073928843663</v>
       </c>
       <c r="AK38" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="AL38" t="n">
         <v>0.145333333333356</v>
@@ -5761,10 +6152,10 @@
         <v>0.803794407609499</v>
       </c>
       <c r="AQ38" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="AR38" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="AS38" t="n">
         <v>12.7465</v>
@@ -5787,13 +6178,13 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B39" t="n">
         <v>0.000262304679650516</v>
       </c>
       <c r="C39" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="D39" t="n">
         <v>-0.745999999999952</v>
@@ -5811,10 +6202,10 @@
         <v>0.314103775336781</v>
       </c>
       <c r="I39" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="J39" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="K39" t="n">
         <v>22.339333333333</v>
@@ -5835,13 +6226,13 @@
         <v>1</v>
       </c>
       <c r="R39" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="S39" t="n">
         <v>0.103848010309764</v>
       </c>
       <c r="T39" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="U39" t="n">
         <v>-0.0140000000000194</v>
@@ -5859,10 +6250,10 @@
         <v>0.969270424184002</v>
       </c>
       <c r="Z39" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="AA39" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="AB39" t="n">
         <v>18.0978333333334</v>
@@ -5883,13 +6274,13 @@
         <v>1</v>
       </c>
       <c r="AI39" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="AJ39" t="n">
         <v>0.00000000000000000000219073928843663</v>
       </c>
       <c r="AK39" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="AL39" t="n">
         <v>-0.474333333333389</v>
@@ -5907,10 +6298,10 @@
         <v>0.420357662840351</v>
       </c>
       <c r="AQ39" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="AR39" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="AS39" t="n">
         <v>12.7465</v>
@@ -5933,13 +6324,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B40" t="n">
         <v>0.000262304679650516</v>
       </c>
       <c r="C40" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="D40" t="n">
         <v>-0.783333333333313</v>
@@ -5957,10 +6348,10 @@
         <v>0.291022844649224</v>
       </c>
       <c r="I40" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="J40" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="K40" t="n">
         <v>22.339333333333</v>
@@ -5981,13 +6372,13 @@
         <v>1</v>
       </c>
       <c r="R40" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="S40" t="n">
         <v>0.103848010309764</v>
       </c>
       <c r="T40" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="U40" t="n">
         <v>-0.0619999999999928</v>
@@ -6005,10 +6396,10 @@
         <v>0.864574906888322</v>
       </c>
       <c r="Z40" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="AA40" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="AB40" t="n">
         <v>18.0978333333334</v>
@@ -6029,13 +6420,13 @@
         <v>1</v>
       </c>
       <c r="AI40" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="AJ40" t="n">
         <v>0.00000000000000000000219073928843663</v>
       </c>
       <c r="AK40" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="AL40" t="n">
         <v>-5.26283333333336</v>
@@ -6053,10 +6444,10 @@
         <v>0.00000000302029138348937</v>
       </c>
       <c r="AQ40" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="AR40" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="AS40" t="n">
         <v>12.7465</v>
@@ -6079,13 +6470,13 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B41" t="n">
         <v>0.000262304679650516</v>
       </c>
       <c r="C41" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="D41" t="n">
         <v>2.65099999999997</v>
@@ -6103,10 +6494,10 @@
         <v>0.00125710815776197</v>
       </c>
       <c r="I41" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="J41" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="K41" t="n">
         <v>22.339333333333</v>
@@ -6127,13 +6518,13 @@
         <v>0.0439987855216688</v>
       </c>
       <c r="R41" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="S41" t="n">
         <v>0.103848010309764</v>
       </c>
       <c r="T41" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="U41" t="n">
         <v>1.02116666666666</v>
@@ -6151,10 +6542,10 @@
         <v>0.0090595138600761</v>
       </c>
       <c r="Z41" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="AA41" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="AB41" t="n">
         <v>18.0978333333334</v>
@@ -6175,13 +6566,13 @@
         <v>0.308023471242587</v>
       </c>
       <c r="AI41" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="AJ41" t="n">
         <v>0.00000000000000000000219073928843663</v>
       </c>
       <c r="AK41" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="AL41" t="n">
         <v>9.54916666666663</v>
@@ -6199,10 +6590,10 @@
         <v>0.0000000000000132938925454852</v>
       </c>
       <c r="AQ41" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="AR41" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="AS41" t="n">
         <v>12.7465</v>
@@ -6225,13 +6616,13 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B42" t="n">
         <v>0.000262304679650516</v>
       </c>
       <c r="C42" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="D42" t="n">
         <v>0.386666666666694</v>
@@ -6249,10 +6640,10 @@
         <v>0.598975308467436</v>
       </c>
       <c r="I42" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="J42" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="K42" t="n">
         <v>22.339333333333</v>
@@ -6273,13 +6664,13 @@
         <v>1</v>
       </c>
       <c r="R42" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="S42" t="n">
         <v>0.103848010309764</v>
       </c>
       <c r="T42" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="U42" t="n">
         <v>-0.07383333333334</v>
@@ -6297,10 +6688,10 @@
         <v>0.839073169384838</v>
       </c>
       <c r="Z42" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="AA42" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="AB42" t="n">
         <v>18.0978333333334</v>
@@ -6321,13 +6712,13 @@
         <v>1</v>
       </c>
       <c r="AI42" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="AJ42" t="n">
         <v>0.00000000000000000000219073928843663</v>
       </c>
       <c r="AK42" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="AL42" t="n">
         <v>5.0014999999999</v>
@@ -6345,10 +6736,10 @@
         <v>0.00000000778826043165535</v>
       </c>
       <c r="AQ42" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="AR42" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="AS42" t="n">
         <v>12.7465</v>
@@ -6371,13 +6762,13 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B43" t="n">
         <v>0.000262304679650516</v>
       </c>
       <c r="C43" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="D43" t="n">
         <v>1.91683333333325</v>
@@ -6395,10 +6786,10 @@
         <v>0.0142790967307209</v>
       </c>
       <c r="I43" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="J43" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="K43" t="n">
         <v>22.339333333333</v>
@@ -6419,13 +6810,13 @@
         <v>0.45693109538307</v>
       </c>
       <c r="R43" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="S43" t="n">
         <v>0.103848010309764</v>
       </c>
       <c r="T43" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="U43" t="n">
         <v>0.660500000000032</v>
@@ -6443,10 +6834,10 @@
         <v>0.0786968206340767</v>
       </c>
       <c r="Z43" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="AA43" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="AB43" t="n">
         <v>18.0978333333334</v>
@@ -6467,13 +6858,13 @@
         <v>1</v>
       </c>
       <c r="AI43" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="AJ43" t="n">
         <v>0.00000000000000000000219073928843663</v>
       </c>
       <c r="AK43" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="AL43" t="n">
         <v>9.4278333333333</v>
@@ -6491,10 +6882,10 @@
         <v>0.0000000000000176374755380997</v>
       </c>
       <c r="AQ43" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="AR43" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="AS43" t="n">
         <v>12.7465</v>
@@ -6517,13 +6908,13 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B44" t="n">
         <v>0.000262304679650516</v>
       </c>
       <c r="C44" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="D44" t="n">
         <v>0.505333333333274</v>
@@ -6541,10 +6932,10 @@
         <v>0.49280794588621</v>
       </c>
       <c r="I44" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J44" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="K44" t="n">
         <v>23.2546666666664</v>
@@ -6565,13 +6956,13 @@
         <v>1</v>
       </c>
       <c r="R44" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="S44" t="n">
         <v>0.103848010309764</v>
       </c>
       <c r="T44" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="U44" t="n">
         <v>-0.234500000000016</v>
@@ -6589,10 +6980,10 @@
         <v>0.520577480969421</v>
       </c>
       <c r="Z44" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AA44" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="AB44" t="n">
         <v>17.9766666666668</v>
@@ -6613,13 +7004,13 @@
         <v>1</v>
       </c>
       <c r="AI44" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="AJ44" t="n">
         <v>0.00000000000000000000219073928843663</v>
       </c>
       <c r="AK44" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="AL44" t="n">
         <v>0.653333333333364</v>
@@ -6637,10 +7028,10 @@
         <v>0.269946192212881</v>
       </c>
       <c r="AQ44" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AR44" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="AS44" t="n">
         <v>13.2545</v>
@@ -6663,13 +7054,13 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B45" t="n">
         <v>0.000262304679650516</v>
       </c>
       <c r="C45" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="D45" t="n">
         <v>-0.335999999999899</v>
@@ -6687,10 +7078,10 @@
         <v>0.647459635754858</v>
       </c>
       <c r="I45" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="J45" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="K45" t="n">
         <v>22.7493333333331</v>
@@ -6711,13 +7102,13 @@
         <v>1</v>
       </c>
       <c r="R45" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="S45" t="n">
         <v>0.103848010309764</v>
       </c>
       <c r="T45" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="U45" t="n">
         <v>0.0993333333333624</v>
@@ -6735,10 +7126,10 @@
         <v>0.78476059484822</v>
       </c>
       <c r="Z45" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="AA45" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="AB45" t="n">
         <v>18.2111666666668</v>
@@ -6759,13 +7150,13 @@
         <v>1</v>
       </c>
       <c r="AI45" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="AJ45" t="n">
         <v>0.00000000000000000000219073928843663</v>
       </c>
       <c r="AK45" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="AL45" t="n">
         <v>-0.619666666666745</v>
@@ -6783,10 +7174,10 @@
         <v>0.294788746112358</v>
       </c>
       <c r="AQ45" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="AR45" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="AS45" t="n">
         <v>12.6011666666666</v>
@@ -6809,13 +7200,13 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B46" t="n">
         <v>0.000262304679650516</v>
       </c>
       <c r="C46" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="D46" t="n">
         <v>-0.373333333333259</v>
@@ -6833,10 +7224,10 @@
         <v>0.611564474354217</v>
       </c>
       <c r="I46" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="J46" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="K46" t="n">
         <v>22.7493333333331</v>
@@ -6857,13 +7248,13 @@
         <v>1</v>
       </c>
       <c r="R46" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="S46" t="n">
         <v>0.103848010309764</v>
       </c>
       <c r="T46" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="U46" t="n">
         <v>0.051333333333389</v>
@@ -6881,10 +7272,10 @@
         <v>0.88769250905937</v>
       </c>
       <c r="Z46" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="AA46" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="AB46" t="n">
         <v>18.2111666666668</v>
@@ -6905,13 +7296,13 @@
         <v>1</v>
       </c>
       <c r="AI46" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="AJ46" t="n">
         <v>0.00000000000000000000219073928843663</v>
       </c>
       <c r="AK46" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="AL46" t="n">
         <v>-5.40816666666672</v>
@@ -6929,10 +7320,10 @@
         <v>0.00000000180409496134564</v>
       </c>
       <c r="AQ46" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="AR46" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="AS46" t="n">
         <v>12.6011666666666</v>
@@ -6955,13 +7346,13 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B47" t="n">
         <v>0.000262304679650516</v>
       </c>
       <c r="C47" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="D47" t="n">
         <v>3.06100000000003</v>
@@ -6979,10 +7370,10 @@
         <v>0.000302587828880762</v>
       </c>
       <c r="I47" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="J47" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="K47" t="n">
         <v>22.7493333333331</v>
@@ -7003,13 +7394,13 @@
         <v>0.0108931618397074</v>
       </c>
       <c r="R47" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="S47" t="n">
         <v>0.103848010309764</v>
       </c>
       <c r="T47" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="U47" t="n">
         <v>1.13450000000004</v>
@@ -7027,10 +7418,10 @@
         <v>0.00428705553420544</v>
       </c>
       <c r="Z47" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="AA47" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="AB47" t="n">
         <v>18.2111666666668</v>
@@ -7051,13 +7442,13 @@
         <v>0.154333999231396</v>
       </c>
       <c r="AI47" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="AJ47" t="n">
         <v>0.00000000000000000000219073928843663</v>
       </c>
       <c r="AK47" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="AL47" t="n">
         <v>9.40383333333328</v>
@@ -7075,10 +7466,10 @@
         <v>0.0000000000000186586796229044</v>
       </c>
       <c r="AQ47" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="AR47" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="AS47" t="n">
         <v>12.6011666666666</v>
@@ -7101,13 +7492,13 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B48" t="n">
         <v>0.000262304679650516</v>
       </c>
       <c r="C48" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="D48" t="n">
         <v>0.796666666666747</v>
@@ -7125,10 +7516,10 @@
         <v>0.283080722313288</v>
       </c>
       <c r="I48" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="J48" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="K48" t="n">
         <v>22.7493333333331</v>
@@ -7149,13 +7540,13 @@
         <v>1</v>
       </c>
       <c r="R48" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="S48" t="n">
         <v>0.103848010309764</v>
       </c>
       <c r="T48" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="U48" t="n">
         <v>0.0395000000000418</v>
@@ -7173,10 +7564,10 @@
         <v>0.913457137763557</v>
       </c>
       <c r="Z48" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="AA48" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="AB48" t="n">
         <v>18.2111666666668</v>
@@ -7197,13 +7588,13 @@
         <v>1</v>
       </c>
       <c r="AI48" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="AJ48" t="n">
         <v>0.00000000000000000000219073928843663</v>
       </c>
       <c r="AK48" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="AL48" t="n">
         <v>4.85616666666654</v>
@@ -7221,10 +7612,10 @@
         <v>0.0000000133438124964883</v>
       </c>
       <c r="AQ48" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="AR48" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="AS48" t="n">
         <v>12.6011666666666</v>
@@ -7247,13 +7638,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B49" t="n">
         <v>0.000262304679650516</v>
       </c>
       <c r="C49" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="D49" t="n">
         <v>2.32683333333331</v>
@@ -7271,10 +7662,10 @@
         <v>0.00377555658045315</v>
       </c>
       <c r="I49" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="J49" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="K49" t="n">
         <v>22.7493333333331</v>
@@ -7295,13 +7686,13 @@
         <v>0.128368923735407</v>
       </c>
       <c r="R49" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="S49" t="n">
         <v>0.103848010309764</v>
       </c>
       <c r="T49" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="U49" t="n">
         <v>0.773833333333414</v>
@@ -7319,10 +7710,10 @@
         <v>0.0416997066266199</v>
       </c>
       <c r="Z49" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="AA49" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="AB49" t="n">
         <v>18.2111666666668</v>
@@ -7343,13 +7734,13 @@
         <v>1</v>
       </c>
       <c r="AI49" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="AJ49" t="n">
         <v>0.00000000000000000000219073928843663</v>
       </c>
       <c r="AK49" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="AL49" t="n">
         <v>9.28249999999994</v>
@@ -7367,10 +7758,10 @@
         <v>0.0000000000000248467073912988</v>
       </c>
       <c r="AQ49" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="AR49" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="AS49" t="n">
         <v>12.6011666666666</v>
@@ -7393,13 +7784,13 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B50" t="n">
         <v>0.000262304679650516</v>
       </c>
       <c r="C50" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="D50" t="n">
         <v>-2.26433333333328</v>
@@ -7417,10 +7808,10 @@
         <v>0.00464802305682128</v>
       </c>
       <c r="I50" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="J50" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="K50" t="n">
         <v>19.6883333333331</v>
@@ -7441,13 +7832,13 @@
         <v>0.153384760875102</v>
       </c>
       <c r="R50" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="S50" t="n">
         <v>0.103848010309764</v>
       </c>
       <c r="T50" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="U50" t="n">
         <v>-1.095</v>
@@ -7465,10 +7856,10 @@
         <v>0.00557956916542708</v>
       </c>
       <c r="Z50" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="AA50" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="AB50" t="n">
         <v>17.0766666666667</v>
@@ -7489,13 +7880,13 @@
         <v>0.195284920789948</v>
       </c>
       <c r="AI50" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="AJ50" t="n">
         <v>0.00000000000000000000219073928843663</v>
       </c>
       <c r="AK50" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="AL50" t="n">
         <v>-4.54766666666673</v>
@@ -7513,10 +7904,10 @@
         <v>0.0000000430262874127371</v>
       </c>
       <c r="AQ50" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="AR50" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="AS50" t="n">
         <v>3.19733333333334</v>
@@ -7539,13 +7930,13 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B51" t="n">
         <v>0.000262304679650516</v>
       </c>
       <c r="C51" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="D51" t="n">
         <v>-0.734166666666718</v>
@@ -7563,10 +7954,10 @@
         <v>0.321680274274634</v>
       </c>
       <c r="I51" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="J51" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="K51" t="n">
         <v>19.6883333333331</v>
@@ -7587,13 +7978,13 @@
         <v>1</v>
       </c>
       <c r="R51" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="S51" t="n">
         <v>0.103848010309764</v>
       </c>
       <c r="T51" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="U51" t="n">
         <v>-0.360666666666627</v>
@@ -7611,10 +8002,10 @@
         <v>0.325942912700088</v>
       </c>
       <c r="Z51" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="AA51" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="AB51" t="n">
         <v>17.0766666666667</v>
@@ -7635,13 +8026,13 @@
         <v>1</v>
       </c>
       <c r="AI51" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="AJ51" t="n">
         <v>0.00000000000000000000219073928843663</v>
       </c>
       <c r="AK51" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="AL51" t="n">
         <v>-0.121333333333331</v>
@@ -7659,10 +8050,10 @@
         <v>0.835655430351111</v>
       </c>
       <c r="AQ51" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="AR51" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="AS51" t="n">
         <v>3.19733333333334</v>
@@ -7685,13 +8076,13 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B52" t="n">
         <v>0.000262304679650516</v>
       </c>
       <c r="C52" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="D52" t="n">
         <v>1.53016666666656</v>
@@ -7709,10 +8100,10 @@
         <v>0.0455638594507975</v>
       </c>
       <c r="I52" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="J52" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="K52" t="n">
         <v>21.9526666666663</v>
@@ -7733,13 +8124,13 @@
         <v>1</v>
       </c>
       <c r="R52" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="S52" t="n">
         <v>0.103848010309764</v>
       </c>
       <c r="T52" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="U52" t="n">
         <v>0.734333333333372</v>
@@ -7757,10 +8148,10 @@
         <v>0.0523072612895634</v>
       </c>
       <c r="Z52" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="AA52" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="AB52" t="n">
         <v>18.1716666666667</v>
@@ -7781,13 +8172,13 @@
         <v>1</v>
       </c>
       <c r="AI52" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="AJ52" t="n">
         <v>0.00000000000000000000219073928843663</v>
       </c>
       <c r="AK52" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="AL52" t="n">
         <v>4.4263333333334</v>
@@ -7805,10 +8196,10 @@
         <v>0.0000000688987138891682</v>
       </c>
       <c r="AQ52" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="AR52" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="AS52" t="n">
         <v>7.74500000000007</v>
@@ -7880,7 +8271,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -7899,7 +8290,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -7917,7 +8308,7 @@
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
       <c r="R2" s="2" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="S2" s="2"/>
       <c r="T2" s="2"/>
@@ -8043,7 +8434,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B6" t="n">
         <v>1659.31802261004</v>
@@ -8064,7 +8455,7 @@
         <v>0.000000000000000000000000000000000000000999448338810867</v>
       </c>
       <c r="R6" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="S6" t="n">
         <v>177.581348657049</v>
@@ -8087,7 +8478,7 @@
     </row>
     <row r="7">
       <c r="R7" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="S7" t="n">
         <v>281.346865120152</v>
@@ -8110,7 +8501,7 @@
     </row>
     <row r="8">
       <c r="R8" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="S8" t="n">
         <v>209.464875507895</v>
@@ -8422,18 +8813,18 @@
         <v>38</v>
       </c>
       <c r="P17" s="4" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B18" t="n">
         <v>0.000000000000000000000000000000000000000999448338810867</v>
       </c>
       <c r="C18" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="D18" t="n">
         <v>8.88299032069069</v>
@@ -8451,10 +8842,10 @@
         <v>0.0000000000000000000000020596211435748</v>
       </c>
       <c r="I18" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="J18" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="K18" t="n">
         <v>72373936.5555547</v>
@@ -8469,7 +8860,7 @@
         <v>12.8154460839251</v>
       </c>
       <c r="O18" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="P18" t="n">
         <v>0.0000000000000000000000391328017279212</v>
@@ -8497,13 +8888,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B19" t="n">
         <v>0.000000000000000000000000000000000000000999448338810867</v>
       </c>
       <c r="C19" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D19" t="n">
         <v>-0.391390404665022</v>
@@ -8521,10 +8912,10 @@
         <v>0.52291085215711</v>
       </c>
       <c r="I19" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="J19" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="K19" t="n">
         <v>72373936.5555547</v>
@@ -8575,10 +8966,10 @@
         <v>33</v>
       </c>
       <c r="AB19" s="4" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="AC19" s="4" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="AD19" s="4" t="s">
         <v>34</v>
@@ -8596,18 +8987,18 @@
         <v>38</v>
       </c>
       <c r="AI19" s="4" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B20" t="n">
         <v>0.000000000000000000000000000000000000000999448338810867</v>
       </c>
       <c r="C20" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="D20" t="n">
         <v>-0.532323639933177</v>
@@ -8625,10 +9016,10 @@
         <v>0.384830019889019</v>
       </c>
       <c r="I20" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="J20" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="K20" t="n">
         <v>72373936.5555547</v>
@@ -8649,13 +9040,13 @@
         <v>1</v>
       </c>
       <c r="R20" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="S20" t="n">
         <v>0.0000000000000000722284411194025</v>
       </c>
       <c r="T20" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="U20" t="n">
         <v>0.561442777326066</v>
@@ -8673,13 +9064,13 @@
         <v>0.299304501397841</v>
       </c>
       <c r="Z20" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="AA20" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="AB20" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="AC20"/>
       <c r="AD20" t="n">
@@ -8703,13 +9094,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B21" t="n">
         <v>0.000000000000000000000000000000000000000999448338810867</v>
       </c>
       <c r="C21" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="D21" t="n">
         <v>0.544108684814563</v>
@@ -8727,10 +9118,10 @@
         <v>0.37512560130774</v>
       </c>
       <c r="I21" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="J21" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="K21" t="n">
         <v>72373936.5555547</v>
@@ -8751,13 +9142,13 @@
         <v>1</v>
       </c>
       <c r="R21" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="S21" t="n">
         <v>0.0000000000000000722284411194025</v>
       </c>
       <c r="T21" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="U21" t="n">
         <v>0.409619523330919</v>
@@ -8775,13 +9166,13 @@
         <v>0.447619831220213</v>
       </c>
       <c r="Z21" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="AA21" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="AB21" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="AC21"/>
       <c r="AD21" t="n">
@@ -8805,13 +9196,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B22" t="n">
         <v>0.000000000000000000000000000000000000000999448338810867</v>
       </c>
       <c r="C22" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="D22" t="n">
         <v>-0.433346533663879</v>
@@ -8829,10 +9220,10 @@
         <v>0.478875322326052</v>
       </c>
       <c r="I22" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="J22" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="K22" t="n">
         <v>72373936.5555547</v>
@@ -8853,13 +9244,13 @@
         <v>1</v>
       </c>
       <c r="R22" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="S22" t="n">
         <v>0.0000000000000000722284411194025</v>
       </c>
       <c r="T22" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="U22" t="n">
         <v>0.528966361875259</v>
@@ -8877,13 +9268,13 @@
         <v>0.32780392659516</v>
       </c>
       <c r="Z22" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="AA22" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="AB22" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="AC22"/>
       <c r="AD22" t="n">
@@ -8907,13 +9298,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B23" t="n">
         <v>0.000000000000000000000000000000000000000999448338810867</v>
       </c>
       <c r="C23" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="D23" t="n">
         <v>7.74183256879583</v>
@@ -8931,10 +9322,10 @@
         <v>0.000000000000000000108775796124641</v>
       </c>
       <c r="I23" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="J23" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="K23" t="n">
         <v>72373936.5555547</v>
@@ -8949,19 +9340,19 @@
         <v>11.1691034543944</v>
       </c>
       <c r="O23" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="P23" t="n">
         <v>0.00000000000000000152286114574497</v>
       </c>
       <c r="R23" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="S23" t="n">
         <v>0.0000000000000000722284411194025</v>
       </c>
       <c r="T23" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="U23" t="n">
         <v>-6.55296984720104</v>
@@ -8979,13 +9370,13 @@
         <v>0.000000000000000614330064448215</v>
       </c>
       <c r="Z23" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="AA23" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="AB23" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="AC23"/>
       <c r="AD23" t="n">
@@ -9001,7 +9392,7 @@
         <v>-9.45393710165184</v>
       </c>
       <c r="AH23" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="AI23" t="n">
         <v>0.00000000000000614330064448215</v>
@@ -9009,13 +9400,13 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B24" t="n">
         <v>0.000000000000000000000000000000000000000999448338810867</v>
       </c>
       <c r="C24" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="D24" t="n">
         <v>1.81002555512964</v>
@@ -9033,10 +9424,10 @@
         <v>0.00410402575284826</v>
       </c>
       <c r="I24" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="J24" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="K24" t="n">
         <v>72373936.5555547</v>
@@ -9051,19 +9442,19 @@
         <v>2.61131489226783</v>
       </c>
       <c r="O24" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="P24" t="n">
         <v>0.0492483090341791</v>
       </c>
       <c r="R24" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="S24" t="n">
         <v>0.0000000000000000722284411194025</v>
       </c>
       <c r="T24" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="U24" t="n">
         <v>-8.84693842047013</v>
@@ -9081,13 +9472,13 @@
         <v>0.00000000000000000000940627769080287</v>
       </c>
       <c r="Z24" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="AA24" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="AB24" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="AC24"/>
       <c r="AD24" t="n">
@@ -9103,7 +9494,7 @@
         <v>-12.7634341862623</v>
       </c>
       <c r="AH24" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="AI24" t="n">
         <v>0.000000000000000000118351175711822</v>
@@ -9111,13 +9502,13 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B25" t="n">
         <v>0.000000000000000000000000000000000000000999448338810867</v>
       </c>
       <c r="C25" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="D25" t="n">
         <v>-0.66242136628757</v>
@@ -9135,10 +9526,10 @@
         <v>0.280910788987679</v>
       </c>
       <c r="I25" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="J25" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="K25" t="n">
         <v>72373936.5555547</v>
@@ -9159,13 +9550,13 @@
         <v>1</v>
       </c>
       <c r="R25" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="S25" t="n">
         <v>0.0000000000000000722284411194025</v>
       </c>
       <c r="T25" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="U25" t="n">
         <v>-0.615346859021258</v>
@@ -9183,13 +9574,13 @@
         <v>0.255869067976921</v>
       </c>
       <c r="Z25" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="AA25" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="AB25" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="AC25"/>
       <c r="AD25" t="n">
@@ -9213,13 +9604,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B26" t="n">
         <v>0.000000000000000000000000000000000000000999448338810867</v>
       </c>
       <c r="C26" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="D26" t="n">
         <v>-0.787099607542505</v>
@@ -9237,10 +9628,10 @@
         <v>0.200279069242848</v>
       </c>
       <c r="I26" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="J26" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="K26" t="n">
         <v>72373936.5555547</v>
@@ -9261,13 +9652,13 @@
         <v>1</v>
       </c>
       <c r="R26" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="S26" t="n">
         <v>0.0000000000000000722284411194025</v>
       </c>
       <c r="T26" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="U26" t="n">
         <v>-3.69895255288216</v>
@@ -9285,13 +9676,13 @@
         <v>0.0000000134836865491698</v>
       </c>
       <c r="Z26" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="AA26" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="AB26" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="AC26"/>
       <c r="AD26" t="n">
@@ -9307,7 +9698,7 @@
         <v>-5.33646050452667</v>
       </c>
       <c r="AH26" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="AI26" t="n">
         <v>0.000000107869492393358</v>
@@ -9315,13 +9706,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B27" t="n">
         <v>0.000000000000000000000000000000000000000999448338810867</v>
       </c>
       <c r="C27" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="D27" t="n">
         <v>9.44653172672546</v>
@@ -9339,10 +9730,10 @@
         <v>0.00000000000000000000000417543342965058</v>
       </c>
       <c r="I27" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="J27" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="K27" t="n">
         <v>72373936.5555547</v>
@@ -9357,19 +9748,19 @@
         <v>13.6284644757471</v>
       </c>
       <c r="O27" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="P27" t="n">
         <v>0.0000000000000000000000709823683040599</v>
       </c>
       <c r="R27" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="S27" t="n">
         <v>0.0000000000000000000021519029276224</v>
       </c>
       <c r="T27" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="U27" t="n">
         <v>8.85439349530908</v>
@@ -9387,14 +9778,14 @@
         <v>0.00000000000000000000910393659321705</v>
       </c>
       <c r="Z27" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="AA27" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="AB27"/>
       <c r="AC27" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="AD27" t="n">
         <v>92586244.8533783</v>
@@ -9409,7 +9800,7 @@
         <v>12.7741895857619</v>
       </c>
       <c r="AH27" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="AI27" t="n">
         <v>0.000000000000000000118351175711822</v>
@@ -9417,13 +9808,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B28" t="n">
         <v>0.000000000000000000000000000000000000000999448338810867</v>
       </c>
       <c r="C28" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="D28" t="n">
         <v>8.48204701705059</v>
@@ -9441,10 +9832,10 @@
         <v>0.00000000000000000000116381481840855</v>
       </c>
       <c r="I28" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="J28" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="K28" t="n">
         <v>72373936.5555547</v>
@@ -9459,19 +9850,19 @@
         <v>12.2370071680859</v>
       </c>
       <c r="O28" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="P28" t="n">
         <v>0.0000000000000000000186210370945369</v>
       </c>
       <c r="R28" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="S28" t="n">
         <v>0.0000000000000000000021519029276224</v>
       </c>
       <c r="T28" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="U28" t="n">
         <v>3.99184267311194</v>
@@ -9489,14 +9880,14 @@
         <v>0.00000000208786875357298</v>
       </c>
       <c r="Z28" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="AA28" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="AB28"/>
       <c r="AC28" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="AD28" t="n">
         <v>92586244.8533783</v>
@@ -9511,7 +9902,7 @@
         <v>5.75901162850754</v>
       </c>
       <c r="AH28" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="AI28" t="n">
         <v>0.0000000187908187821568</v>
@@ -9519,13 +9910,13 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B29" t="n">
         <v>0.000000000000000000000000000000000000000999448338810867</v>
       </c>
       <c r="C29" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="D29" t="n">
         <v>10.5429466223477</v>
@@ -9543,10 +9934,10 @@
         <v>0.0000000000000000000000000101471352579656</v>
       </c>
       <c r="I29" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="J29" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="K29" t="n">
         <v>72373936.5555547</v>
@@ -9561,19 +9952,19 @@
         <v>15.2102568084181</v>
       </c>
       <c r="O29" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="P29" t="n">
         <v>0.000000000000000000000000213089840417277</v>
       </c>
       <c r="R29" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="S29" t="n">
         <v>0.0000000000000000000021519029276224</v>
       </c>
       <c r="T29" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="U29" t="n">
         <v>1.73998087078198</v>
@@ -9591,14 +9982,14 @@
         <v>0.00216151196748795</v>
       </c>
       <c r="Z29" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="AA29" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="AB29"/>
       <c r="AC29" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="AD29" t="n">
         <v>52809854.3963501</v>
@@ -9613,7 +10004,7 @@
         <v>2.51026177351882</v>
       </c>
       <c r="AH29" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="AI29" t="n">
         <v>0.0151305837724156</v>
@@ -9621,13 +10012,13 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B30" t="n">
         <v>0.000000000000000000000000000000000000000999448338810867</v>
       </c>
       <c r="C30" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="D30" t="n">
         <v>0.884553461227994</v>
@@ -9645,10 +10036,10 @@
         <v>0.150698800301406</v>
       </c>
       <c r="I30" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="J30" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="K30" t="n">
         <v>72373936.5555547</v>
@@ -9669,13 +10060,13 @@
         <v>1</v>
       </c>
       <c r="R30" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="S30" t="n">
         <v>0.0000000000000000000021519029276224</v>
       </c>
       <c r="T30" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="U30" t="n">
         <v>-0.402164448491964</v>
@@ -9693,14 +10084,14 @@
         <v>0.45587595777157</v>
       </c>
       <c r="Z30" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="AA30" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="AB30"/>
       <c r="AC30" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="AD30" t="n">
         <v>61468267.3491566</v>
@@ -9723,13 +10114,13 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B31" t="n">
         <v>0.000000000000000000000000000000000000000999448338810867</v>
       </c>
       <c r="C31" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="D31" t="n">
         <v>-1.14115775189486</v>
@@ -9747,10 +10138,10 @@
         <v>0.0654257867699021</v>
       </c>
       <c r="I31" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="J31" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="K31" t="n">
         <v>10040.3422320853</v>
@@ -9771,13 +10162,13 @@
         <v>0.654257867699021</v>
       </c>
       <c r="R31" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="S31" t="n">
         <v>0.0000000000000000000021519029276224</v>
       </c>
       <c r="T31" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="U31" t="n">
         <v>7.71008027441257</v>
@@ -9795,14 +10186,14 @@
         <v>0.00000000000000000175053440496271</v>
       </c>
       <c r="Z31" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="AA31" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="AB31"/>
       <c r="AC31" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="AD31" t="n">
         <v>54553082.8583895</v>
@@ -9817,7 +10208,7 @@
         <v>11.1232945767508</v>
       </c>
       <c r="AH31" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="AI31" t="n">
         <v>0.0000000000000000192558784545898</v>
@@ -9825,13 +10216,13 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B32" t="n">
         <v>0.000000000000000000000000000000000000000999448338810867</v>
       </c>
       <c r="C32" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="D32" t="n">
         <v>-7.07296476556105</v>
@@ -9849,10 +10240,10 @@
         <v>0.0000000000000000076853637419842</v>
       </c>
       <c r="I32" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="J32" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="K32" t="n">
         <v>10040.3422320853</v>
@@ -9867,19 +10258,19 @@
         <v>-10.2041311916573</v>
       </c>
       <c r="O32" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="P32" t="n">
         <v>0.0000000000000000999097286457945</v>
       </c>
       <c r="R32" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="S32" t="n">
         <v>0.0000000000000000000021519029276224</v>
       </c>
       <c r="T32" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="U32" t="n">
         <v>-0.236076241645483</v>
@@ -9897,14 +10288,14 @@
         <v>0.660948089229146</v>
       </c>
       <c r="Z32" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="AA32" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="AB32"/>
       <c r="AC32" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="AD32" t="n">
         <v>54553082.8583895</v>
@@ -9927,13 +10318,13 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B33" t="n">
         <v>0.000000000000000000000000000000000000000999448338810867</v>
       </c>
       <c r="C33" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="D33" t="n">
         <v>-9.54541168697826</v>
@@ -9951,10 +10342,10 @@
         <v>0.0000000000000000000000023867733689879</v>
       </c>
       <c r="I33" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="J33" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="K33" t="n">
         <v>10040.3422320853</v>
@@ -9969,7 +10360,7 @@
         <v>-13.7711181040471</v>
       </c>
       <c r="O33" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="P33" t="n">
         <v>0.0000000000000000000000429619206417821</v>
@@ -9977,13 +10368,13 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B34" t="n">
         <v>0.000000000000000000000000000000000000000999448338810867</v>
       </c>
       <c r="C34" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="D34" t="n">
         <v>-9.6700899282332</v>
@@ -10001,10 +10392,10 @@
         <v>0.00000000000000000000000130581915989736</v>
       </c>
       <c r="I34" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="J34" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="K34" t="n">
         <v>10040.3422320853</v>
@@ -10019,7 +10410,7 @@
         <v>-13.9509907844123</v>
       </c>
       <c r="O34" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="P34" t="n">
         <v>0.0000000000000000000000261163831979473</v>
@@ -10027,13 +10418,13 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B35" t="n">
         <v>0.000000000000000000000000000000000000000999448338810867</v>
       </c>
       <c r="C35" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="D35" t="n">
         <v>0.563541406034767</v>
@@ -10051,10 +10442,10 @@
         <v>0.358410830489464</v>
       </c>
       <c r="I35" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="J35" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="K35" t="n">
         <v>10040.3422320853</v>
@@ -10077,13 +10468,13 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B36" t="n">
         <v>0.000000000000000000000000000000000000000999448338810867</v>
       </c>
       <c r="C36" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="D36" t="n">
         <v>-0.400943303640105</v>
@@ -10101,10 +10492,10 @@
         <v>0.512847861490858</v>
       </c>
       <c r="I36" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="J36" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="K36" t="n">
         <v>10040.3422320853</v>
@@ -10127,13 +10518,13 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B37" t="n">
         <v>0.000000000000000000000000000000000000000999448338810867</v>
       </c>
       <c r="C37" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="D37" t="n">
         <v>1.65995630165701</v>
@@ -10151,10 +10542,10 @@
         <v>0.00818467381375133</v>
       </c>
       <c r="I37" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="J37" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="K37" t="n">
         <v>10040.3422320853</v>
@@ -10177,13 +10568,13 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B38" t="n">
         <v>0.000000000000000000000000000000000000000999448338810867</v>
       </c>
       <c r="C38" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="D38" t="n">
         <v>-7.9984368594627</v>
@@ -10201,10 +10592,10 @@
         <v>0.0000000000000000000233357433724456</v>
       </c>
       <c r="I38" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="J38" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="K38" t="n">
         <v>10040.3422320853</v>
@@ -10219,7 +10610,7 @@
         <v>-11.5393051920103</v>
       </c>
       <c r="O38" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="P38" t="n">
         <v>0.000000000000000000350036150586685</v>
@@ -10275,7 +10666,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -10294,7 +10685,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -10369,7 +10760,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="B6" t="n">
         <v>0.220640379137276</v>
@@ -10392,7 +10783,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="B7" t="n">
         <v>137.540937783623</v>
@@ -10415,7 +10806,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="B8" t="n">
         <v>0.823561780371193</v>
@@ -10492,7 +10883,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="B13" t="s">
         <v>20</v>
@@ -10583,10 +10974,10 @@
         <v>33</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="M18" s="4" t="s">
         <v>34</v>
@@ -10606,13 +10997,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="B19" t="n">
         <v>0.576340301567132</v>
       </c>
       <c r="C19" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="D19" t="n">
         <v>0.252752008615745</v>
@@ -10630,13 +11021,13 @@
         <v>0.7143508901217</v>
       </c>
       <c r="I19" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="J19" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="K19" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="L19"/>
       <c r="M19" t="n">
@@ -10657,13 +11048,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="B20" t="n">
         <v>0.576340301567132</v>
       </c>
       <c r="C20" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="D20" t="n">
         <v>-0.795142248372172</v>
@@ -10681,13 +11072,13 @@
         <v>0.272693703320178</v>
       </c>
       <c r="I20" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="J20" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="K20" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="L20"/>
       <c r="M20" t="n">
@@ -10708,13 +11099,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="B21" t="n">
         <v>0.000000490218245559036</v>
       </c>
       <c r="C21" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="D21" t="n">
         <v>7.29498687591886</v>
@@ -10732,14 +11123,14 @@
         <v>0.0000322229443336028</v>
       </c>
       <c r="I21" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="J21" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="K21"/>
       <c r="L21" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="M21" t="n">
         <v>54268340.2635169</v>
@@ -10759,13 +11150,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="B22" t="n">
         <v>0.000000490218245559036</v>
       </c>
       <c r="C22" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="D22" t="n">
         <v>6.24709261893094</v>
@@ -10783,14 +11174,14 @@
         <v>0.0000781728658939154</v>
       </c>
       <c r="I22" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="J22" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="K22"/>
       <c r="L22" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="M22" t="n">
         <v>42148074.2778464</v>
@@ -10857,7 +11248,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -10876,7 +11267,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -10894,7 +11285,7 @@
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
       <c r="R2" s="2" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="S2" s="2"/>
       <c r="T2" s="2"/>
@@ -10912,7 +11303,7 @@
       <c r="AF2" s="2"/>
       <c r="AG2" s="2"/>
       <c r="AI2" s="2" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="AJ2" s="2"/>
       <c r="AK2" s="2"/>
@@ -11080,7 +11471,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="B6" t="n">
         <v>134.487046213518</v>
@@ -11101,7 +11492,7 @@
         <v>0.0047553552107894</v>
       </c>
       <c r="R6" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="S6" t="n">
         <v>0.000634161719309005</v>
@@ -11122,7 +11513,7 @@
         <v>0.775209368586456</v>
       </c>
       <c r="AI6" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="AJ6" t="n">
         <v>1.03769747822441</v>
@@ -11312,7 +11703,7 @@
         <v>1</v>
       </c>
       <c r="R11" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="S11" t="s">
         <v>20</v>
@@ -11331,7 +11722,7 @@
         <v>1</v>
       </c>
       <c r="AI11" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="AJ11" t="s">
         <v>20</v>
@@ -11527,7 +11918,7 @@
         <v>38</v>
       </c>
       <c r="AG16" s="4" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="AI16" s="4" t="s">
         <v>24</v>
@@ -11575,7 +11966,7 @@
         <v>38</v>
       </c>
       <c r="AX16" s="4" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17">
@@ -11625,16 +12016,16 @@
         <v>38</v>
       </c>
       <c r="P17" s="4" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="R17" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="S17" t="n">
         <v>0.775209368586456</v>
       </c>
       <c r="T17" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="U17" t="n">
         <v>-0.0244297817001489</v>
@@ -11652,10 +12043,10 @@
         <v>1</v>
       </c>
       <c r="Z17" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="AA17" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="AB17" t="n">
         <v>0.882883029161526</v>
@@ -11676,13 +12067,13 @@
         <v>1</v>
       </c>
       <c r="AI17" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="AJ17" t="n">
         <v>0.0000187353382347323</v>
       </c>
       <c r="AK17" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="AL17" t="n">
         <v>-0.67070741915742</v>
@@ -11700,10 +12091,10 @@
         <v>0.0000408578448097907</v>
       </c>
       <c r="AQ17" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="AR17" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="AS17" t="n">
         <v>0.991798545298763</v>
@@ -11726,13 +12117,13 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="B18" t="n">
         <v>0.0047553552107894</v>
       </c>
       <c r="C18" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="D18" t="n">
         <v>-7.11736948659326</v>
@@ -11750,10 +12141,10 @@
         <v>0.0230393047842817</v>
       </c>
       <c r="I18" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="J18" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="K18" t="n">
         <v>0.96994074702232</v>
@@ -11774,13 +12165,13 @@
         <v>0.0460786095685635</v>
       </c>
       <c r="R18" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="S18" t="n">
         <v>0.775209368586456</v>
       </c>
       <c r="T18" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="U18" t="n">
         <v>-0.00692238539008128</v>
@@ -11798,10 +12189,10 @@
         <v>1</v>
       </c>
       <c r="Z18" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="AA18" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="AB18" t="n">
         <v>0.882883029161526</v>
@@ -11816,13 +12207,13 @@
         <v>1</v>
       </c>
       <c r="AI18" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="AJ18" t="n">
         <v>0.0000187353382347323</v>
       </c>
       <c r="AK18" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="AL18" t="n">
         <v>-0.377111511969424</v>
@@ -11840,10 +12231,10 @@
         <v>0.00177775146105684</v>
       </c>
       <c r="AQ18" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="AR18" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="AS18" t="n">
         <v>0.991798545298763</v>
@@ -11866,13 +12257,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="B19" t="n">
         <v>0.0047553552107894</v>
       </c>
       <c r="C19" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="D19" t="n">
         <v>-0.0316561038392367</v>
@@ -11890,10 +12281,10 @@
         <v>0.986608105599029</v>
       </c>
       <c r="I19" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="J19" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="K19" t="n">
         <v>0.96994074702232</v>
@@ -11908,13 +12299,13 @@
         <v>0.986608105599029</v>
       </c>
       <c r="AI19" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="AJ19" t="n">
         <v>0.0000187353382347323</v>
       </c>
       <c r="AK19" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="AL19" t="n">
         <v>0.0244095963564464</v>
@@ -11932,10 +12323,10 @@
         <v>0.71342047319382</v>
       </c>
       <c r="AQ19" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="AR19" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="AS19" t="n">
         <v>0.991798545298763</v>
